--- a/SuppXLS/Scen_UC_SOLHEAT_MANHEAT_10_25.xlsx
+++ b/SuppXLS/Scen_UC_SOLHEAT_MANHEAT_10_25.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D9EE8E-FB7C-4524-AEF2-2E445D70FEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E3D5EE-0E13-4172-8C71-DC88927DF65E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
   <sheets>
-    <sheet name="SOLHEAT_10_25" sheetId="1" r:id="rId1"/>
+    <sheet name="SOLTHT_10_25" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -104,13 +104,13 @@
     <t>MANHEAT</t>
   </si>
   <si>
-    <t>SOLAR</t>
-  </si>
-  <si>
     <t>Minimum SOLHEAT  penetration for process heat</t>
   </si>
   <si>
-    <t>UC_SOLHEAT_10_25</t>
+    <t>SOLTHT</t>
+  </si>
+  <si>
+    <t>UC_SOLTHT_10_25</t>
   </si>
 </sst>
 </file>
@@ -712,7 +712,7 @@
       </c>
       <c r="D6" s="8"/>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
         <v>21</v>
@@ -739,7 +739,7 @@
         <v>15</v>
       </c>
       <c r="O6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -751,7 +751,7 @@
       </c>
       <c r="D7" s="8"/>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
         <v>21</v>
@@ -778,7 +778,7 @@
         <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
